--- a/organograma_modelo.xlsx
+++ b/organograma_modelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\izadora.guardiano\Desktop\organograma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{840080F7-1A32-46C7-B851-3FF6CF1F3921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B61E194-F5FA-4A4B-9830-C1631BB96BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-2940" windowWidth="24240" windowHeight="13020" xr2:uid="{D38C0BA7-EA9C-448B-8F9A-A359ADF13E09}"/>
   </bookViews>
@@ -845,74 +845,74 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -953,7 +953,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1273961</xdr:colOff>
+      <xdr:colOff>1277771</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>148591</xdr:rowOff>
     </xdr:to>
@@ -1311,15 +1311,15 @@
     <row r="2" spans="2:10" ht="37.200000000000003" x14ac:dyDescent="0.3">
       <c r="B2" s="22"/>
       <c r="C2" s="27"/>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="47"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="45"/>
     </row>
     <row r="3" spans="2:10" ht="19.8" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
@@ -1335,16 +1335,16 @@
       <c r="H3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="49"/>
+      <c r="I3" s="47"/>
       <c r="J3" s="52"/>
     </row>
     <row r="4" spans="2:10" ht="19.8" x14ac:dyDescent="0.3">
       <c r="B4" s="5"/>
       <c r="C4" s="16"/>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="49"/>
+      <c r="E4" s="47"/>
       <c r="F4" s="53"/>
       <c r="G4" s="53"/>
       <c r="H4" s="53"/>
@@ -1354,10 +1354,10 @@
     <row r="5" spans="2:10" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="26"/>
       <c r="C5" s="28"/>
-      <c r="D5" s="50" t="s">
+      <c r="D5" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="51"/>
+      <c r="E5" s="49"/>
       <c r="F5" s="55"/>
       <c r="G5" s="55"/>
       <c r="H5" s="55"/>
@@ -1380,11 +1380,11 @@
       <c r="J6" s="24"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="20"/>
       <c r="F7" s="20"/>
       <c r="G7" s="20"/>
@@ -1405,24 +1405,24 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="11"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="62"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
       <c r="J9" s="16"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="12"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="62"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="42"/>
       <c r="J10" s="16"/>
     </row>
     <row r="11" spans="2:10" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1452,11 +1452,11 @@
       <c r="J12" s="24"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
       <c r="E13" s="20"/>
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
@@ -1489,10 +1489,10 @@
       <c r="F15" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="44" t="s">
+      <c r="G15" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="44"/>
+      <c r="H15" s="57"/>
       <c r="I15" s="17" t="s">
         <v>13</v>
       </c>
@@ -1504,8 +1504,8 @@
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
       <c r="I16" s="17"/>
       <c r="J16" s="8"/>
     </row>
@@ -1536,11 +1536,11 @@
       <c r="J18" s="24"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
       <c r="E19" s="20"/>
       <c r="F19" s="20"/>
       <c r="G19" s="20"/>
@@ -1573,11 +1573,11 @@
       <c r="F21" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="40" t="s">
+      <c r="G21" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40"/>
+      <c r="H21" s="58"/>
+      <c r="I21" s="58"/>
       <c r="J21" s="8"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
@@ -1586,9 +1586,9 @@
       <c r="D22" s="37"/>
       <c r="E22" s="37"/>
       <c r="F22" s="37"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="58"/>
       <c r="J22" s="8"/>
     </row>
     <row r="23" spans="2:10" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1618,10 +1618,10 @@
       <c r="J24" s="24"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="43"/>
+      <c r="C25" s="51"/>
       <c r="D25" s="20"/>
       <c r="E25" s="20"/>
       <c r="F25" s="20"/>
@@ -1645,8 +1645,8 @@
       <c r="B27" s="12"/>
       <c r="C27" s="37"/>
       <c r="D27" s="37"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="58"/>
       <c r="G27" s="6"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -1656,8 +1656,8 @@
       <c r="B28" s="12"/>
       <c r="C28" s="37"/>
       <c r="D28" s="37"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="58"/>
       <c r="G28" s="6"/>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -1675,10 +1675,10 @@
       <c r="J29" s="35"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B30" s="42" t="s">
+      <c r="B30" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="43"/>
+      <c r="C30" s="51"/>
       <c r="D30" s="20"/>
       <c r="E30" s="20"/>
       <c r="F30" s="20"/>
@@ -1702,8 +1702,8 @@
       <c r="B32" s="12"/>
       <c r="C32" s="39"/>
       <c r="D32" s="39"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
       <c r="G32" s="6"/>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -1713,8 +1713,8 @@
       <c r="B33" s="12"/>
       <c r="C33" s="39"/>
       <c r="D33" s="39"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="59"/>
       <c r="G33" s="6"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -1743,7 +1743,18 @@
       <c r="J35" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="19">
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="G22:I22"/>
     <mergeCell ref="D2:J2"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D5:E5"/>
@@ -1752,20 +1763,6 @@
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="F4:J4"/>
     <mergeCell ref="F5:J5"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions gridLines="1"/>
